--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -418,7 +418,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2561" uniqueCount="1457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1462">
   <si>
     <t>_id</t>
   </si>
@@ -4116,10 +4116,25 @@
     <t>19,20,21,22,23,24</t>
   </si>
   <si>
+    <t>508</t>
+  </si>
+  <si>
+    <t>虚无专属</t>
+  </si>
+  <si>
+    <t>25,26,27,28,29,30</t>
+  </si>
+  <si>
+    <t>601</t>
+  </si>
+  <si>
     <t>宝石随机</t>
   </si>
   <si>
     <t>60000001,60000002,60000003,60000004,60000005,60000006,60000007,60000008,60000009,60000010</t>
+  </si>
+  <si>
+    <t>602</t>
   </si>
   <si>
     <t>极宝石随机</t>
@@ -16731,22 +16746,34 @@
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="3"/>
+      <c r="C19" s="18" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>1234</v>
+      </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C20" s="1">
-        <v>601</v>
+      <c r="C20" s="18" t="s">
+        <v>1235</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -16755,18 +16782,18 @@
         <v>5</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>1233</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C21" s="1">
-        <v>602</v>
+      <c r="C21" s="18" t="s">
+        <v>1238</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1234</v>
+        <v>1239</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
@@ -16775,7 +16802,7 @@
         <v>5</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>1235</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16794,121 +16821,121 @@
         <v>1118</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1240</v>
+        <v>1245</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>21</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>1241</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>1244</v>
+        <v>1249</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1245</v>
+        <v>1250</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>1246</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>1247</v>
+        <v>1252</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1248</v>
+        <v>1253</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>1250</v>
+        <v>1255</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1251</v>
+        <v>1256</v>
       </c>
       <c r="F28" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>1252</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>1253</v>
+        <v>1258</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>1118</v>
@@ -16928,62 +16955,62 @@
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>1254</v>
+        <v>1259</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="F30" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>1256</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="F31" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>1259</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>1260</v>
+        <v>1265</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>1262</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -16994,16 +17021,16 @@
         <v>1118</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1263</v>
+        <v>1268</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>1264</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -17014,176 +17041,176 @@
         <v>1118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1265</v>
+        <v>1270</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>1266</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>1269</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1271</v>
+        <v>1276</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>1272</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1274</v>
+        <v>1279</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>1275</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>1278</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>1281</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>1284</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>1285</v>
+        <v>1290</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>1286</v>
+        <v>1291</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>1287</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>1289</v>
+        <v>1294</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>1290</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17194,36 +17221,36 @@
         <v>1118</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1291</v>
+        <v>1296</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17236,7 +17263,7 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1118</v>
@@ -17256,7 +17283,7 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1118</v>
@@ -17276,13 +17303,13 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1298</v>
+        <v>1303</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1299</v>
+        <v>1304</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>17</v>
@@ -17291,12 +17318,12 @@
         <v>1120</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>1300</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>1118</v>
@@ -17316,13 +17343,13 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1302</v>
+        <v>1307</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1303</v>
+        <v>1308</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>17</v>
@@ -17331,18 +17358,18 @@
         <v>1120</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="F51" s="18" t="s">
         <v>17</v>
@@ -17351,18 +17378,18 @@
         <v>1120</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>1307</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="18" t="s">
-        <v>1308</v>
+        <v>1313</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="F52" s="18" t="s">
         <v>17</v>
@@ -17371,18 +17398,18 @@
         <v>1120</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>1310</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1311</v>
+        <v>1316</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>17</v>
@@ -17391,7 +17418,7 @@
         <v>1120</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -17402,7 +17429,7 @@
         <v>1118</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1314</v>
+        <v>1319</v>
       </c>
       <c r="F54" s="18" t="s">
         <v>17</v>
@@ -17411,7 +17438,7 @@
         <v>1120</v>
       </c>
       <c r="H54" s="25" t="s">
-        <v>1315</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -17422,7 +17449,7 @@
         <v>1118</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1316</v>
+        <v>1321</v>
       </c>
       <c r="F55" s="18" t="s">
         <v>17</v>
@@ -17431,18 +17458,18 @@
         <v>1120</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>1317</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1318</v>
+        <v>1323</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1319</v>
+        <v>1324</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>17</v>
@@ -17451,18 +17478,18 @@
         <v>1120</v>
       </c>
       <c r="H56" s="25" t="s">
-        <v>1320</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>1321</v>
+        <v>1326</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1322</v>
+        <v>1327</v>
       </c>
       <c r="F57" s="18" t="s">
         <v>17</v>
@@ -17471,18 +17498,18 @@
         <v>1120</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>1323</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>1324</v>
+        <v>1329</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1325</v>
+        <v>1330</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>17</v>
@@ -17491,18 +17518,18 @@
         <v>1120</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>1326</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>17</v>
@@ -17511,18 +17538,18 @@
         <v>1120</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>1329</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="18" t="s">
-        <v>1330</v>
+        <v>1335</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1331</v>
+        <v>1336</v>
       </c>
       <c r="F60" s="18" t="s">
         <v>17</v>
@@ -17531,18 +17558,18 @@
         <v>1120</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>1332</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="18" t="s">
-        <v>1333</v>
+        <v>1338</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="F61" s="18" t="s">
         <v>17</v>
@@ -17551,18 +17578,18 @@
         <v>1120</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>1335</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="18" t="s">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>17</v>
@@ -17571,18 +17598,18 @@
         <v>1120</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>1338</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="18" t="s">
-        <v>1339</v>
+        <v>1344</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1340</v>
+        <v>1345</v>
       </c>
       <c r="F63" s="18" t="s">
         <v>17</v>
@@ -17591,18 +17618,18 @@
         <v>1120</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>1341</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="18" t="s">
-        <v>1342</v>
+        <v>1347</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>1343</v>
+        <v>1348</v>
       </c>
       <c r="F64" s="18" t="s">
         <v>17</v>
@@ -17611,18 +17638,18 @@
         <v>1120</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>1344</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="18" t="s">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
       <c r="F65" s="18" t="s">
         <v>17</v>
@@ -17631,18 +17658,18 @@
         <v>1120</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="18" t="s">
-        <v>1348</v>
+        <v>1353</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1349</v>
+        <v>1354</v>
       </c>
       <c r="F66" s="18" t="s">
         <v>17</v>
@@ -17651,7 +17678,7 @@
         <v>1120</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>1350</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17670,7 +17697,7 @@
         <v>0</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="F68" s="18" t="s">
         <v>17</v>
@@ -17679,7 +17706,7 @@
         <v>25</v>
       </c>
       <c r="H68" s="24" t="s">
-        <v>1352</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17690,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="F69" s="18" t="s">
         <v>17</v>
@@ -17699,7 +17726,7 @@
         <v>25</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17710,7 +17737,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1355</v>
+        <v>1360</v>
       </c>
       <c r="F70" s="18" t="s">
         <v>17</v>
@@ -17719,7 +17746,7 @@
         <v>25</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>1356</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17730,7 +17757,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1357</v>
+        <v>1362</v>
       </c>
       <c r="F71" s="18" t="s">
         <v>17</v>
@@ -17739,7 +17766,7 @@
         <v>25</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17750,7 +17777,7 @@
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1359</v>
+        <v>1364</v>
       </c>
       <c r="F72" s="18" t="s">
         <v>17</v>
@@ -17759,7 +17786,7 @@
         <v>25</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>1360</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17770,7 +17797,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1361</v>
+        <v>1366</v>
       </c>
       <c r="F73" s="18" t="s">
         <v>17</v>
@@ -17779,7 +17806,7 @@
         <v>25</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>1362</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17790,7 +17817,7 @@
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="F74" s="18" t="s">
         <v>17</v>
@@ -17799,7 +17826,7 @@
         <v>25</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>1364</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17810,7 +17837,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="F75" s="18" t="s">
         <v>17</v>
@@ -17819,7 +17846,7 @@
         <v>25</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>1366</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17830,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1367</v>
+        <v>1372</v>
       </c>
       <c r="F76" s="18" t="s">
         <v>17</v>
@@ -17839,7 +17866,7 @@
         <v>25</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>1368</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17850,7 +17877,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="F77" s="18" t="s">
         <v>17</v>
@@ -17859,7 +17886,7 @@
         <v>25</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>1370</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17870,7 +17897,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1371</v>
+        <v>1376</v>
       </c>
       <c r="F78" s="18" t="s">
         <v>17</v>
@@ -17879,7 +17906,7 @@
         <v>25</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>1372</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17890,7 +17917,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1373</v>
+        <v>1378</v>
       </c>
       <c r="F79" s="18" t="s">
         <v>17</v>
@@ -17899,7 +17926,7 @@
         <v>25</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>1374</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17910,7 +17937,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1375</v>
+        <v>1380</v>
       </c>
       <c r="F80" s="18" t="s">
         <v>17</v>
@@ -17919,7 +17946,7 @@
         <v>25</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17930,7 +17957,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1377</v>
+        <v>1382</v>
       </c>
       <c r="F81" s="18" t="s">
         <v>17</v>
@@ -17939,7 +17966,7 @@
         <v>25</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>1378</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17950,7 +17977,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1379</v>
+        <v>1384</v>
       </c>
       <c r="F82" s="18" t="s">
         <v>17</v>
@@ -17959,7 +17986,7 @@
         <v>25</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>1380</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="83" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17970,7 +17997,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1381</v>
+        <v>1386</v>
       </c>
       <c r="F83" s="18" t="s">
         <v>17</v>
@@ -17979,7 +18006,7 @@
         <v>25</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>1382</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17990,7 +18017,7 @@
         <v>0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="F84" s="18" t="s">
         <v>17</v>
@@ -17999,7 +18026,7 @@
         <v>25</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>1384</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="85" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18010,7 +18037,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1385</v>
+        <v>1390</v>
       </c>
       <c r="F85" s="18" t="s">
         <v>17</v>
@@ -18019,7 +18046,7 @@
         <v>25</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>1386</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="86" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18030,7 +18057,7 @@
         <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1387</v>
+        <v>1392</v>
       </c>
       <c r="F86" s="18" t="s">
         <v>17</v>
@@ -18039,7 +18066,7 @@
         <v>25</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>1388</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="87" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18050,7 +18077,7 @@
         <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1389</v>
+        <v>1394</v>
       </c>
       <c r="F87" s="18" t="s">
         <v>17</v>
@@ -18059,7 +18086,7 @@
         <v>25</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>1390</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="88" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18070,7 +18097,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1391</v>
+        <v>1396</v>
       </c>
       <c r="F88" s="18" t="s">
         <v>17</v>
@@ -18079,7 +18106,7 @@
         <v>25</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>1392</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18090,7 +18117,7 @@
         <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1393</v>
+        <v>1398</v>
       </c>
       <c r="F89" s="18" t="s">
         <v>17</v>
@@ -18099,7 +18126,7 @@
         <v>25</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>1394</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="90" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18110,7 +18137,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="F90" s="18" t="s">
         <v>17</v>
@@ -18119,7 +18146,7 @@
         <v>25</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>1396</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="91" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18130,7 +18157,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="F91" s="18" t="s">
         <v>17</v>
@@ -18139,7 +18166,7 @@
         <v>25</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>1398</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18158,7 +18185,7 @@
         <v>0</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="F93" s="18" t="s">
         <v>17</v>
@@ -18167,7 +18194,7 @@
         <v>25</v>
       </c>
       <c r="H93" s="24" t="s">
-        <v>1399</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="94" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18178,7 +18205,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1385</v>
+        <v>1390</v>
       </c>
       <c r="F94" s="18" t="s">
         <v>17</v>
@@ -18187,7 +18214,7 @@
         <v>25</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>1400</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="95" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18198,7 +18225,7 @@
         <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1387</v>
+        <v>1392</v>
       </c>
       <c r="F95" s="18" t="s">
         <v>17</v>
@@ -18207,7 +18234,7 @@
         <v>25</v>
       </c>
       <c r="H95" s="24" t="s">
-        <v>1401</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="96" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18218,7 +18245,7 @@
         <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>1389</v>
+        <v>1394</v>
       </c>
       <c r="F96" s="18" t="s">
         <v>17</v>
@@ -18227,7 +18254,7 @@
         <v>25</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>1402</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="97" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18238,7 +18265,7 @@
         <v>0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1391</v>
+        <v>1396</v>
       </c>
       <c r="F97" s="18" t="s">
         <v>17</v>
@@ -18247,7 +18274,7 @@
         <v>25</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>1403</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="98" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18258,7 +18285,7 @@
         <v>0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>1393</v>
+        <v>1398</v>
       </c>
       <c r="F98" s="18" t="s">
         <v>17</v>
@@ -18267,7 +18294,7 @@
         <v>25</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>1404</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="99" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18278,7 +18305,7 @@
         <v>0</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="F99" s="18" t="s">
         <v>17</v>
@@ -18287,7 +18314,7 @@
         <v>25</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>1405</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="100" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18298,7 +18325,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1397</v>
+        <v>1402</v>
       </c>
       <c r="F100" s="18" t="s">
         <v>17</v>
@@ -18307,7 +18334,7 @@
         <v>25</v>
       </c>
       <c r="H100" s="24" t="s">
-        <v>1406</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="101" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18328,7 +18355,7 @@
     </row>
     <row r="103" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C103" s="18" t="s">
-        <v>1407</v>
+        <v>1412</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>1118</v>
@@ -18348,7 +18375,7 @@
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C104" s="18" t="s">
-        <v>1408</v>
+        <v>1413</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>1118</v>
@@ -18368,13 +18395,13 @@
     </row>
     <row r="105" customHeight="1" spans="3:8">
       <c r="C105" s="18" t="s">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>1410</v>
+        <v>1415</v>
       </c>
       <c r="F105" s="18" t="s">
         <v>17</v>
@@ -18383,18 +18410,18 @@
         <v>1130</v>
       </c>
       <c r="H105" s="22" t="s">
-        <v>1411</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:8">
       <c r="C106" s="18" t="s">
-        <v>1412</v>
+        <v>1417</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1413</v>
+        <v>1418</v>
       </c>
       <c r="F106" s="18" t="s">
         <v>17</v>
@@ -18403,18 +18430,18 @@
         <v>1130</v>
       </c>
       <c r="H106" s="22" t="s">
-        <v>1414</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:8">
       <c r="C107" s="18" t="s">
-        <v>1415</v>
+        <v>1420</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>1416</v>
+        <v>1421</v>
       </c>
       <c r="F107" s="18" t="s">
         <v>17</v>
@@ -18423,18 +18450,18 @@
         <v>1130</v>
       </c>
       <c r="H107" s="22" t="s">
-        <v>1417</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:8">
       <c r="C108" s="18" t="s">
-        <v>1418</v>
+        <v>1423</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>1419</v>
+        <v>1424</v>
       </c>
       <c r="F108" s="18" t="s">
         <v>17</v>
@@ -18443,47 +18470,47 @@
         <v>1130</v>
       </c>
       <c r="H108" s="22" t="s">
-        <v>1420</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:8">
       <c r="C110" s="18" t="s">
-        <v>1421</v>
+        <v>1426</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>1422</v>
+        <v>1427</v>
       </c>
       <c r="F110" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G110" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H110" s="22" t="s">
-        <v>1423</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:8">
       <c r="C111" s="18" t="s">
-        <v>1424</v>
+        <v>1429</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>1425</v>
+        <v>1430</v>
       </c>
       <c r="F111" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G111" s="18" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="H111" s="22" t="s">
-        <v>1426</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="112" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18496,182 +18523,182 @@
     </row>
     <row r="113" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C113" s="10" t="s">
-        <v>1427</v>
+        <v>1432</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>1428</v>
+        <v>1433</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="H113" s="18" t="s">
-        <v>1430</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="114" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C114" s="10" t="s">
-        <v>1431</v>
+        <v>1436</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>1432</v>
+        <v>1437</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="H114" s="18" t="s">
-        <v>1433</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C115" s="10" t="s">
-        <v>1434</v>
+        <v>1439</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>1435</v>
+        <v>1440</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="H115" s="18" t="s">
-        <v>1436</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C116" s="10" t="s">
-        <v>1437</v>
+        <v>1442</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>1438</v>
+        <v>1443</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="H116" s="18" t="s">
-        <v>1439</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="117" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C117" s="10" t="s">
-        <v>1440</v>
+        <v>1445</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>1441</v>
+        <v>1446</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="H117" s="18" t="s">
-        <v>1442</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="118" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C118" s="10" t="s">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>1444</v>
+        <v>1449</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="H118" s="18" t="s">
-        <v>1445</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="119" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C119" s="10" t="s">
-        <v>1446</v>
+        <v>1451</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>1447</v>
+        <v>1452</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="H119" s="18" t="s">
-        <v>1448</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="120" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C120" s="10" t="s">
-        <v>1449</v>
+        <v>1454</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>1450</v>
+        <v>1455</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="H120" s="24" t="s">
-        <v>1451</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C121" s="10" t="s">
-        <v>1452</v>
+        <v>1457</v>
       </c>
       <c r="D121" s="18" t="s">
         <v>47</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>1453</v>
+        <v>1458</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="H121" s="24" t="s">
-        <v>1454</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -18682,16 +18709,16 @@
         <v>100</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>1455</v>
+        <v>1460</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="H122" s="24" t="s">
-        <v>1456</v>
+        <v>1461</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -418,7 +418,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2575" uniqueCount="1465">
   <si>
     <t>_id</t>
   </si>
@@ -4486,6 +4486,15 @@
   </si>
   <si>
     <t>1998001,1998002,1998003,1998004,1998005</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>粉色图鉴</t>
+  </si>
+  <si>
+    <t>1998006,1998007,1998008,1998009,1998010</t>
   </si>
   <si>
     <t>绿色英灵</t>
@@ -16405,7 +16414,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H122"/>
+  <dimension ref="C1:H123"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -17681,43 +17690,43 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="3"/>
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C67" s="18" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F67" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G67" s="18" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H67" s="24" t="s">
+        <v>1358</v>
+      </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C68" s="1">
-        <v>2031</v>
-      </c>
-      <c r="D68" s="1">
-        <v>0</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>1356</v>
-      </c>
-      <c r="F68" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G68" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H68" s="24" t="s">
-        <v>1357</v>
-      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="3"/>
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C69" s="1">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="F69" s="18" t="s">
         <v>17</v>
@@ -17726,18 +17735,18 @@
         <v>25</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C70" s="1">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F70" s="18" t="s">
         <v>17</v>
@@ -17746,18 +17755,18 @@
         <v>25</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C71" s="1">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="F71" s="18" t="s">
         <v>17</v>
@@ -17766,18 +17775,18 @@
         <v>25</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C72" s="1">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="F72" s="18" t="s">
         <v>17</v>
@@ -17786,18 +17795,18 @@
         <v>25</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C73" s="1">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="F73" s="18" t="s">
         <v>17</v>
@@ -17806,18 +17815,18 @@
         <v>25</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C74" s="1">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="F74" s="18" t="s">
         <v>17</v>
@@ -17826,18 +17835,18 @@
         <v>25</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C75" s="1">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="F75" s="18" t="s">
         <v>17</v>
@@ -17846,18 +17855,18 @@
         <v>25</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C76" s="1">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="F76" s="18" t="s">
         <v>17</v>
@@ -17866,18 +17875,18 @@
         <v>25</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C77" s="1">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="F77" s="18" t="s">
         <v>17</v>
@@ -17886,18 +17895,18 @@
         <v>25</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C78" s="1">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="F78" s="18" t="s">
         <v>17</v>
@@ -17906,18 +17915,18 @@
         <v>25</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C79" s="1">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="F79" s="18" t="s">
         <v>17</v>
@@ -17926,18 +17935,18 @@
         <v>25</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C80" s="1">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="F80" s="18" t="s">
         <v>17</v>
@@ -17946,18 +17955,18 @@
         <v>25</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C81" s="1">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="F81" s="18" t="s">
         <v>17</v>
@@ -17966,18 +17975,18 @@
         <v>25</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C82" s="1">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="F82" s="18" t="s">
         <v>17</v>
@@ -17986,18 +17995,18 @@
         <v>25</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="83" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C83" s="1">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="F83" s="18" t="s">
         <v>17</v>
@@ -18006,18 +18015,18 @@
         <v>25</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C84" s="1">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="F84" s="18" t="s">
         <v>17</v>
@@ -18026,18 +18035,18 @@
         <v>25</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="85" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C85" s="1">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="F85" s="18" t="s">
         <v>17</v>
@@ -18046,18 +18055,18 @@
         <v>25</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="86" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C86" s="1">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="F86" s="18" t="s">
         <v>17</v>
@@ -18066,18 +18075,18 @@
         <v>25</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="87" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C87" s="1">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="F87" s="18" t="s">
         <v>17</v>
@@ -18086,18 +18095,18 @@
         <v>25</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="88" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C88" s="1">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="F88" s="18" t="s">
         <v>17</v>
@@ -18106,18 +18115,18 @@
         <v>25</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C89" s="1">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="F89" s="18" t="s">
         <v>17</v>
@@ -18126,18 +18135,18 @@
         <v>25</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="90" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C90" s="1">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F90" s="18" t="s">
         <v>17</v>
@@ -18146,18 +18155,18 @@
         <v>25</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="91" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C91" s="1">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F91" s="18" t="s">
         <v>17</v>
@@ -18166,46 +18175,46 @@
         <v>25</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="3"/>
+      <c r="C92" s="1">
+        <v>2054</v>
+      </c>
+      <c r="D92" s="1">
+        <v>0</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F92" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G92" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H92" s="24" t="s">
+        <v>1406</v>
+      </c>
     </row>
     <row r="93" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C93" s="1">
-        <v>2055</v>
-      </c>
-      <c r="D93" s="1">
-        <v>0</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>1388</v>
-      </c>
-      <c r="F93" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G93" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H93" s="24" t="s">
-        <v>1404</v>
-      </c>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="3"/>
     </row>
     <row r="94" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C94" s="1">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="D94" s="1">
         <v>0</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="F94" s="18" t="s">
         <v>17</v>
@@ -18214,18 +18223,18 @@
         <v>25</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="95" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C95" s="1">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="D95" s="1">
         <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="F95" s="18" t="s">
         <v>17</v>
@@ -18234,18 +18243,18 @@
         <v>25</v>
       </c>
       <c r="H95" s="24" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="96" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C96" s="1">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="D96" s="1">
         <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="F96" s="18" t="s">
         <v>17</v>
@@ -18254,18 +18263,18 @@
         <v>25</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="97" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C97" s="1">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="D97" s="1">
         <v>0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="F97" s="18" t="s">
         <v>17</v>
@@ -18274,18 +18283,18 @@
         <v>25</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="98" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C98" s="1">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="D98" s="1">
         <v>0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="F98" s="18" t="s">
         <v>17</v>
@@ -18294,18 +18303,18 @@
         <v>25</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="99" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C99" s="1">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="D99" s="1">
         <v>0</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="F99" s="18" t="s">
         <v>17</v>
@@ -18314,18 +18323,18 @@
         <v>25</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="100" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C100" s="1">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="D100" s="1">
         <v>0</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="F100" s="18" t="s">
         <v>17</v>
@@ -18334,16 +18343,28 @@
         <v>25</v>
       </c>
       <c r="H100" s="24" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="101" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-      <c r="H101" s="3"/>
+      <c r="C101" s="1">
+        <v>2062</v>
+      </c>
+      <c r="D101" s="1">
+        <v>0</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F101" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H101" s="24" t="s">
+        <v>1414</v>
+      </c>
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C102" s="1"/>
@@ -18353,35 +18374,23 @@
       <c r="G102" s="1"/>
       <c r="H102" s="3"/>
     </row>
-    <row r="103" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C103" s="18" t="s">
-        <v>1412</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F103" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G103" s="18" t="s">
-        <v>1130</v>
-      </c>
-      <c r="H103" s="24" t="s">
-        <v>1131</v>
-      </c>
+    <row r="103" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="3"/>
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C104" s="18" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="F104" s="18" t="s">
         <v>17</v>
@@ -18390,18 +18399,18 @@
         <v>1130</v>
       </c>
       <c r="H104" s="24" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="105" customHeight="1" spans="3:8">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="105" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C105" s="18" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>1415</v>
+        <v>1133</v>
       </c>
       <c r="F105" s="18" t="s">
         <v>17</v>
@@ -18409,8 +18418,8 @@
       <c r="G105" s="18" t="s">
         <v>1130</v>
       </c>
-      <c r="H105" s="22" t="s">
-        <v>1416</v>
+      <c r="H105" s="24" t="s">
+        <v>1134</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:8">
@@ -18473,23 +18482,23 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="110" customHeight="1" spans="3:8">
-      <c r="C110" s="18" t="s">
+    <row r="109" customHeight="1" spans="3:8">
+      <c r="C109" s="18" t="s">
         <v>1426</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D109" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="E109" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="F110" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G110" s="18" t="s">
-        <v>1242</v>
-      </c>
-      <c r="H110" s="22" t="s">
+      <c r="F109" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G109" s="18" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H109" s="22" t="s">
         <v>1428</v>
       </c>
     </row>
@@ -18513,49 +18522,49 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="112" s="2" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1"/>
-      <c r="G112" s="1"/>
-      <c r="H112" s="3"/>
-    </row>
-    <row r="113" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C113" s="10" t="s">
+    <row r="112" customHeight="1" spans="3:8">
+      <c r="C112" s="18" t="s">
         <v>1432</v>
       </c>
-      <c r="D113" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E113" s="1" t="s">
+      <c r="D112" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>1433</v>
       </c>
-      <c r="F113" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G113" s="1" t="s">
+      <c r="F112" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G112" s="18" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H112" s="22" t="s">
         <v>1434</v>
       </c>
-      <c r="H113" s="18" t="s">
-        <v>1435</v>
-      </c>
+    </row>
+    <row r="113" s="2" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="3"/>
     </row>
     <row r="114" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C114" s="10" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E114" s="1" t="s">
+      <c r="F114" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G114" s="1" t="s">
         <v>1437</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>1434</v>
       </c>
       <c r="H114" s="18" t="s">
         <v>1438</v>
@@ -18566,7 +18575,7 @@
         <v>1439</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>1440</v>
@@ -18575,7 +18584,7 @@
         <v>17</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="H115" s="18" t="s">
         <v>1441</v>
@@ -18586,7 +18595,7 @@
         <v>1442</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>1443</v>
@@ -18595,7 +18604,7 @@
         <v>17</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="H116" s="18" t="s">
         <v>1444</v>
@@ -18606,7 +18615,7 @@
         <v>1445</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>1446</v>
@@ -18615,7 +18624,7 @@
         <v>17</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="H117" s="18" t="s">
         <v>1447</v>
@@ -18626,7 +18635,7 @@
         <v>1448</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>1449</v>
@@ -18635,7 +18644,7 @@
         <v>17</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="H118" s="18" t="s">
         <v>1450</v>
@@ -18646,7 +18655,7 @@
         <v>1451</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>1452</v>
@@ -18655,7 +18664,7 @@
         <v>17</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="H119" s="18" t="s">
         <v>1453</v>
@@ -18666,7 +18675,7 @@
         <v>1454</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>1455</v>
@@ -18675,9 +18684,9 @@
         <v>17</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>1434</v>
-      </c>
-      <c r="H120" s="24" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H120" s="18" t="s">
         <v>1456</v>
       </c>
     </row>
@@ -18685,8 +18694,8 @@
       <c r="C121" s="10" t="s">
         <v>1457</v>
       </c>
-      <c r="D121" s="18" t="s">
-        <v>47</v>
+      <c r="D121" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>1458</v>
@@ -18695,30 +18704,50 @@
         <v>17</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="H121" s="24" t="s">
         <v>1459</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C122" s="10">
+      <c r="C122" s="10" t="s">
+        <v>1460</v>
+      </c>
+      <c r="D122" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H122" s="24" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="123" s="1" customFormat="1" customHeight="1" spans="3:8">
+      <c r="C123" s="10">
         <v>300091</v>
       </c>
-      <c r="D122" s="1">
+      <c r="D123" s="1">
         <v>100</v>
       </c>
-      <c r="E122" s="1" t="s">
-        <v>1460</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>1434</v>
-      </c>
-      <c r="H122" s="24" t="s">
-        <v>1461</v>
+      <c r="E123" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H123" s="24" t="s">
+        <v>1464</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="5"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="1" r:id="rId1"/>
@@ -418,7 +418,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2575" uniqueCount="1465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2582" uniqueCount="1471">
   <si>
     <t>_id</t>
   </si>
@@ -3924,6 +3924,18 @@
     <t>190013,190014,190015,190016,190017,190018</t>
   </si>
   <si>
+    <t>220045</t>
+  </si>
+  <si>
+    <t>粉色魂心</t>
+  </si>
+  <si>
+    <t>220046</t>
+  </si>
+  <si>
+    <t>暗金兽魂</t>
+  </si>
+  <si>
     <t>220101</t>
   </si>
   <si>
@@ -4006,6 +4018,12 @@
   </si>
   <si>
     <t>暗金坐骑</t>
+  </si>
+  <si>
+    <t>220309</t>
+  </si>
+  <si>
+    <t>粉色坐骑</t>
   </si>
   <si>
     <t>101</t>
@@ -15269,7 +15287,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H61"/>
+  <dimension ref="C1:H64"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -16109,44 +16127,44 @@
         <v>1167</v>
       </c>
     </row>
+    <row r="44" customHeight="1" spans="3:8">
+      <c r="C44" s="19" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1">
+        <v>5</v>
+      </c>
+      <c r="H44" s="1">
+        <v>4045</v>
+      </c>
+    </row>
     <row r="45" customHeight="1" spans="3:8">
       <c r="C45" s="19" t="s">
-        <v>1168</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>1169</v>
+        <v>1170</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>1171</v>
       </c>
       <c r="F45" s="1">
         <v>1</v>
       </c>
       <c r="G45" s="1">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H45" s="1">
-        <v>8201</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:8">
-      <c r="C46" s="19" t="s">
-        <v>1170</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>1171</v>
-      </c>
-      <c r="F46" s="1">
-        <v>1</v>
-      </c>
-      <c r="G46" s="1">
-        <v>16</v>
-      </c>
-      <c r="H46" s="1">
-        <v>8202</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:8">
@@ -16166,7 +16184,7 @@
         <v>16</v>
       </c>
       <c r="H47" s="1">
-        <v>8203</v>
+        <v>8201</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:8">
@@ -16186,7 +16204,7 @@
         <v>16</v>
       </c>
       <c r="H48" s="1">
-        <v>8204</v>
+        <v>8202</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:8">
@@ -16206,7 +16224,7 @@
         <v>16</v>
       </c>
       <c r="H49" s="1">
-        <v>8205</v>
+        <v>8203</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:8">
@@ -16226,7 +16244,7 @@
         <v>16</v>
       </c>
       <c r="H50" s="1">
-        <v>8206</v>
+        <v>8204</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:8">
@@ -16246,7 +16264,7 @@
         <v>16</v>
       </c>
       <c r="H51" s="1">
-        <v>8207</v>
+        <v>8205</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:8">
@@ -16266,58 +16284,58 @@
         <v>16</v>
       </c>
       <c r="H52" s="1">
+        <v>8206</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:8">
+      <c r="C53" s="19" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F53" s="1">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1">
+        <v>16</v>
+      </c>
+      <c r="H53" s="1">
+        <v>8207</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:8">
+      <c r="C54" s="19" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F54" s="1">
+        <v>1</v>
+      </c>
+      <c r="G54" s="1">
+        <v>16</v>
+      </c>
+      <c r="H54" s="1">
         <v>8209</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="3:8">
-      <c r="C54" s="10"/>
-      <c r="E54" s="12"/>
-      <c r="H54" s="1"/>
-    </row>
-    <row r="55" customHeight="1" spans="3:8">
-      <c r="C55" s="10"/>
-      <c r="E55" s="12"/>
-      <c r="H55" s="1"/>
-    </row>
     <row r="56" customHeight="1" spans="3:8">
-      <c r="C56" s="19" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>1185</v>
-      </c>
-      <c r="F56" s="1">
-        <v>1</v>
-      </c>
-      <c r="G56" s="1">
-        <v>31</v>
-      </c>
-      <c r="H56" s="1">
-        <v>8303</v>
-      </c>
+      <c r="C56" s="10"/>
+      <c r="E56" s="12"/>
+      <c r="H56" s="1"/>
     </row>
     <row r="57" customHeight="1" spans="3:8">
-      <c r="C57" s="19" t="s">
-        <v>1186</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>1187</v>
-      </c>
-      <c r="F57" s="1">
-        <v>1</v>
-      </c>
-      <c r="G57" s="1">
-        <v>31</v>
-      </c>
-      <c r="H57" s="1">
-        <v>8304</v>
-      </c>
+      <c r="C57" s="10"/>
+      <c r="E57" s="12"/>
+      <c r="H57" s="1"/>
     </row>
     <row r="58" customHeight="1" spans="3:8">
       <c r="C58" s="19" t="s">
@@ -16336,7 +16354,7 @@
         <v>31</v>
       </c>
       <c r="H58" s="1">
-        <v>8305</v>
+        <v>8303</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:8">
@@ -16356,7 +16374,7 @@
         <v>31</v>
       </c>
       <c r="H59" s="1">
-        <v>8306</v>
+        <v>8304</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:8">
@@ -16376,7 +16394,7 @@
         <v>31</v>
       </c>
       <c r="H60" s="1">
-        <v>8307</v>
+        <v>8305</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:8">
@@ -16396,7 +16414,67 @@
         <v>31</v>
       </c>
       <c r="H61" s="1">
+        <v>8306</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:8">
+      <c r="C62" s="19" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F62" s="1">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1">
+        <v>31</v>
+      </c>
+      <c r="H62" s="1">
+        <v>8307</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:8">
+      <c r="C63" s="19" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F63" s="1">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1">
+        <v>31</v>
+      </c>
+      <c r="H63" s="1">
         <v>8308</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:8">
+      <c r="C64" s="19" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F64" s="1">
+        <v>1</v>
+      </c>
+      <c r="G64" s="1">
+        <v>31</v>
+      </c>
+      <c r="H64" s="1">
+        <v>8309</v>
       </c>
     </row>
   </sheetData>
@@ -16496,13 +16574,13 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C6" s="1" t="s">
-        <v>1196</v>
+        <v>1202</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>17</v>
@@ -16511,18 +16589,18 @@
         <v>18</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1198</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C7" s="18" t="s">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>17</v>
@@ -16531,18 +16609,18 @@
         <v>18</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>1201</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C8" s="18" t="s">
-        <v>1202</v>
+        <v>1208</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1203</v>
+        <v>1209</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>17</v>
@@ -16551,18 +16629,18 @@
         <v>18</v>
       </c>
       <c r="H8" s="24" t="s">
-        <v>1204</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C9" s="18" t="s">
-        <v>1205</v>
+        <v>1211</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1206</v>
+        <v>1212</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>17</v>
@@ -16571,18 +16649,18 @@
         <v>18</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>1207</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C10" s="18" t="s">
-        <v>1208</v>
+        <v>1214</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1209</v>
+        <v>1215</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>17</v>
@@ -16591,18 +16669,18 @@
         <v>18</v>
       </c>
       <c r="H10" s="24" t="s">
-        <v>1210</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C11" s="18" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1212</v>
+        <v>1218</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>17</v>
@@ -16611,18 +16689,18 @@
         <v>18</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>1213</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C12" s="18" t="s">
-        <v>1214</v>
+        <v>1220</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>17</v>
@@ -16631,18 +16709,18 @@
         <v>15</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>1216</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C13" s="18" t="s">
-        <v>1217</v>
+        <v>1223</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>17</v>
@@ -16651,18 +16729,18 @@
         <v>15</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>1218</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C14" s="18" t="s">
-        <v>1219</v>
+        <v>1225</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>17</v>
@@ -16671,18 +16749,18 @@
         <v>15</v>
       </c>
       <c r="H14" s="24" t="s">
-        <v>1220</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C15" s="18" t="s">
-        <v>1221</v>
+        <v>1227</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1215</v>
+        <v>1221</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>17</v>
@@ -16691,18 +16769,18 @@
         <v>15</v>
       </c>
       <c r="H15" s="24" t="s">
-        <v>1222</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C16" s="18" t="s">
-        <v>1223</v>
+        <v>1229</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>17</v>
@@ -16711,18 +16789,18 @@
         <v>15</v>
       </c>
       <c r="H16" s="24" t="s">
-        <v>1225</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C17" s="18" t="s">
-        <v>1226</v>
+        <v>1232</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1227</v>
+        <v>1233</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>17</v>
@@ -16731,18 +16809,18 @@
         <v>15</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>1228</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C18" s="18" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>17</v>
@@ -16751,18 +16829,18 @@
         <v>15</v>
       </c>
       <c r="H18" s="24" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C19" s="18" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1233</v>
+        <v>1239</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>17</v>
@@ -16771,18 +16849,18 @@
         <v>15</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>1234</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C20" s="18" t="s">
-        <v>1235</v>
+        <v>1241</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1236</v>
+        <v>1242</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -16791,18 +16869,18 @@
         <v>5</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>1237</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C21" s="18" t="s">
-        <v>1238</v>
+        <v>1244</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1239</v>
+        <v>1245</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
@@ -16811,7 +16889,7 @@
         <v>5</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -16830,121 +16908,121 @@
         <v>1118</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1241</v>
+        <v>1247</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>18</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H23" s="24" t="s">
-        <v>1243</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C24" s="18" t="s">
-        <v>1244</v>
+        <v>1250</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C25" s="18" t="s">
-        <v>1247</v>
+        <v>1253</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1248</v>
+        <v>1254</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>21</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>1246</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C26" s="18" t="s">
-        <v>1249</v>
+        <v>1255</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1250</v>
+        <v>1256</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>1251</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C27" s="18" t="s">
-        <v>1252</v>
+        <v>1258</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1253</v>
+        <v>1259</v>
       </c>
       <c r="F27" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>1254</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C28" s="18" t="s">
-        <v>1255</v>
+        <v>1261</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="F28" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H28" s="24" t="s">
-        <v>1257</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C29" s="18" t="s">
-        <v>1258</v>
+        <v>1264</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>1118</v>
@@ -16964,62 +17042,62 @@
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C30" s="18" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="F30" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H30" s="24" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C31" s="18" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1263</v>
+        <v>1269</v>
       </c>
       <c r="F31" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>1264</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C32" s="18" t="s">
-        <v>1265</v>
+        <v>1271</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1266</v>
+        <v>1272</v>
       </c>
       <c r="F32" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H32" s="24" t="s">
-        <v>1267</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -17030,16 +17108,16 @@
         <v>1118</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="F33" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>1269</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -17050,176 +17128,176 @@
         <v>1118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="F34" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H34" s="24" t="s">
-        <v>1271</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C35" s="18" t="s">
-        <v>1272</v>
+        <v>1278</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1273</v>
+        <v>1279</v>
       </c>
       <c r="F35" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>1274</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C36" s="18" t="s">
-        <v>1275</v>
+        <v>1281</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1276</v>
+        <v>1282</v>
       </c>
       <c r="F36" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>1277</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C37" s="18" t="s">
-        <v>1278</v>
+        <v>1284</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>1279</v>
+        <v>1285</v>
       </c>
       <c r="F37" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C38" s="18" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="F38" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>1283</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C39" s="18" t="s">
-        <v>1284</v>
+        <v>1290</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1285</v>
+        <v>1291</v>
       </c>
       <c r="F39" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>1286</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C40" s="18" t="s">
-        <v>1287</v>
+        <v>1293</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>1288</v>
+        <v>1294</v>
       </c>
       <c r="F40" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>1289</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C41" s="18" t="s">
-        <v>1290</v>
+        <v>1296</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="F41" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>1292</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C42" s="18" t="s">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>1294</v>
+        <v>1300</v>
       </c>
       <c r="F42" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17230,36 +17308,36 @@
         <v>1118</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="F43" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>1297</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:8">
       <c r="C44" s="18" t="s">
-        <v>1298</v>
+        <v>1304</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>1299</v>
+        <v>1305</v>
       </c>
       <c r="F44" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H44" s="24" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17272,7 +17350,7 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C46" s="18" t="s">
-        <v>1301</v>
+        <v>1307</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>1118</v>
@@ -17292,7 +17370,7 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C47" s="18" t="s">
-        <v>1302</v>
+        <v>1308</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>1118</v>
@@ -17312,13 +17390,13 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C48" s="18" t="s">
-        <v>1303</v>
+        <v>1309</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="F48" s="18" t="s">
         <v>17</v>
@@ -17327,12 +17405,12 @@
         <v>1120</v>
       </c>
       <c r="H48" s="24" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C49" s="18" t="s">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>1118</v>
@@ -17352,13 +17430,13 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C50" s="18" t="s">
-        <v>1307</v>
+        <v>1313</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>1308</v>
+        <v>1314</v>
       </c>
       <c r="F50" s="18" t="s">
         <v>17</v>
@@ -17367,18 +17445,18 @@
         <v>1120</v>
       </c>
       <c r="H50" s="24" t="s">
-        <v>1309</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C51" s="18" t="s">
-        <v>1310</v>
+        <v>1316</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>1311</v>
+        <v>1317</v>
       </c>
       <c r="F51" s="18" t="s">
         <v>17</v>
@@ -17387,18 +17465,18 @@
         <v>1120</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>1312</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C52" s="18" t="s">
-        <v>1313</v>
+        <v>1319</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1314</v>
+        <v>1320</v>
       </c>
       <c r="F52" s="18" t="s">
         <v>17</v>
@@ -17407,18 +17485,18 @@
         <v>1120</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C53" s="18" t="s">
-        <v>1316</v>
+        <v>1322</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1317</v>
+        <v>1323</v>
       </c>
       <c r="F53" s="18" t="s">
         <v>17</v>
@@ -17427,7 +17505,7 @@
         <v>1120</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>1318</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -17438,7 +17516,7 @@
         <v>1118</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>1319</v>
+        <v>1325</v>
       </c>
       <c r="F54" s="18" t="s">
         <v>17</v>
@@ -17447,7 +17525,7 @@
         <v>1120</v>
       </c>
       <c r="H54" s="25" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -17458,7 +17536,7 @@
         <v>1118</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>1321</v>
+        <v>1327</v>
       </c>
       <c r="F55" s="18" t="s">
         <v>17</v>
@@ -17467,18 +17545,18 @@
         <v>1120</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>1322</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C56" s="18" t="s">
-        <v>1323</v>
+        <v>1329</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>1324</v>
+        <v>1330</v>
       </c>
       <c r="F56" s="18" t="s">
         <v>17</v>
@@ -17487,18 +17565,18 @@
         <v>1120</v>
       </c>
       <c r="H56" s="25" t="s">
-        <v>1325</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C57" s="18" t="s">
-        <v>1326</v>
+        <v>1332</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="F57" s="18" t="s">
         <v>17</v>
@@ -17507,18 +17585,18 @@
         <v>1120</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C58" s="18" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="F58" s="18" t="s">
         <v>17</v>
@@ -17527,18 +17605,18 @@
         <v>1120</v>
       </c>
       <c r="H58" s="24" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C59" s="18" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="F59" s="18" t="s">
         <v>17</v>
@@ -17547,18 +17625,18 @@
         <v>1120</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C60" s="18" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="F60" s="18" t="s">
         <v>17</v>
@@ -17567,18 +17645,18 @@
         <v>1120</v>
       </c>
       <c r="H60" s="24" t="s">
-        <v>1337</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C61" s="18" t="s">
-        <v>1338</v>
+        <v>1344</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>1339</v>
+        <v>1345</v>
       </c>
       <c r="F61" s="18" t="s">
         <v>17</v>
@@ -17587,18 +17665,18 @@
         <v>1120</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>1340</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C62" s="18" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1342</v>
+        <v>1348</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>17</v>
@@ -17607,18 +17685,18 @@
         <v>1120</v>
       </c>
       <c r="H62" s="24" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C63" s="18" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="F63" s="18" t="s">
         <v>17</v>
@@ -17627,18 +17705,18 @@
         <v>1120</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>1346</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C64" s="18" t="s">
-        <v>1347</v>
+        <v>1353</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>1348</v>
+        <v>1354</v>
       </c>
       <c r="F64" s="18" t="s">
         <v>17</v>
@@ -17647,18 +17725,18 @@
         <v>1120</v>
       </c>
       <c r="H64" s="24" t="s">
-        <v>1349</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C65" s="18" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>1351</v>
+        <v>1357</v>
       </c>
       <c r="F65" s="18" t="s">
         <v>17</v>
@@ -17667,18 +17745,18 @@
         <v>1120</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>1352</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C66" s="18" t="s">
-        <v>1353</v>
+        <v>1359</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1354</v>
+        <v>1360</v>
       </c>
       <c r="F66" s="18" t="s">
         <v>17</v>
@@ -17687,18 +17765,18 @@
         <v>1120</v>
       </c>
       <c r="H66" s="24" t="s">
-        <v>1355</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C67" s="18" t="s">
-        <v>1356</v>
+        <v>1362</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1357</v>
+        <v>1363</v>
       </c>
       <c r="F67" s="18" t="s">
         <v>17</v>
@@ -17707,7 +17785,7 @@
         <v>1120</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>1358</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17726,7 +17804,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1359</v>
+        <v>1365</v>
       </c>
       <c r="F69" s="18" t="s">
         <v>17</v>
@@ -17735,7 +17813,7 @@
         <v>25</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>1360</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17746,7 +17824,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>1361</v>
+        <v>1367</v>
       </c>
       <c r="F70" s="18" t="s">
         <v>17</v>
@@ -17755,7 +17833,7 @@
         <v>25</v>
       </c>
       <c r="H70" s="24" t="s">
-        <v>1362</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17766,7 +17844,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1363</v>
+        <v>1369</v>
       </c>
       <c r="F71" s="18" t="s">
         <v>17</v>
@@ -17775,7 +17853,7 @@
         <v>25</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>1364</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17786,7 +17864,7 @@
         <v>0</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1365</v>
+        <v>1371</v>
       </c>
       <c r="F72" s="18" t="s">
         <v>17</v>
@@ -17795,7 +17873,7 @@
         <v>25</v>
       </c>
       <c r="H72" s="24" t="s">
-        <v>1366</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17806,7 +17884,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="F73" s="18" t="s">
         <v>17</v>
@@ -17815,7 +17893,7 @@
         <v>25</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>1368</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17826,7 +17904,7 @@
         <v>0</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1369</v>
+        <v>1375</v>
       </c>
       <c r="F74" s="18" t="s">
         <v>17</v>
@@ -17835,7 +17913,7 @@
         <v>25</v>
       </c>
       <c r="H74" s="24" t="s">
-        <v>1370</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17846,7 +17924,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>1371</v>
+        <v>1377</v>
       </c>
       <c r="F75" s="18" t="s">
         <v>17</v>
@@ -17855,7 +17933,7 @@
         <v>25</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>1372</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17866,7 +17944,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1373</v>
+        <v>1379</v>
       </c>
       <c r="F76" s="18" t="s">
         <v>17</v>
@@ -17875,7 +17953,7 @@
         <v>25</v>
       </c>
       <c r="H76" s="24" t="s">
-        <v>1374</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="77" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17886,7 +17964,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1375</v>
+        <v>1381</v>
       </c>
       <c r="F77" s="18" t="s">
         <v>17</v>
@@ -17895,7 +17973,7 @@
         <v>25</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>1376</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="78" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17906,7 +17984,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>1377</v>
+        <v>1383</v>
       </c>
       <c r="F78" s="18" t="s">
         <v>17</v>
@@ -17915,7 +17993,7 @@
         <v>25</v>
       </c>
       <c r="H78" s="24" t="s">
-        <v>1378</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="79" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17926,7 +18004,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1379</v>
+        <v>1385</v>
       </c>
       <c r="F79" s="18" t="s">
         <v>17</v>
@@ -17935,7 +18013,7 @@
         <v>25</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="80" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17946,7 +18024,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1381</v>
+        <v>1387</v>
       </c>
       <c r="F80" s="18" t="s">
         <v>17</v>
@@ -17955,7 +18033,7 @@
         <v>25</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>1382</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="81" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17966,7 +18044,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1383</v>
+        <v>1389</v>
       </c>
       <c r="F81" s="18" t="s">
         <v>17</v>
@@ -17975,7 +18053,7 @@
         <v>25</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>1384</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="82" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -17986,7 +18064,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>1385</v>
+        <v>1391</v>
       </c>
       <c r="F82" s="18" t="s">
         <v>17</v>
@@ -17995,7 +18073,7 @@
         <v>25</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>1386</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="83" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18006,7 +18084,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="F83" s="18" t="s">
         <v>17</v>
@@ -18015,7 +18093,7 @@
         <v>25</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>1388</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="84" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18026,7 +18104,7 @@
         <v>0</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>1389</v>
+        <v>1395</v>
       </c>
       <c r="F84" s="18" t="s">
         <v>17</v>
@@ -18035,7 +18113,7 @@
         <v>25</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>1390</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="85" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18046,7 +18124,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="F85" s="18" t="s">
         <v>17</v>
@@ -18055,7 +18133,7 @@
         <v>25</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>1392</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="86" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18066,7 +18144,7 @@
         <v>0</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="F86" s="18" t="s">
         <v>17</v>
@@ -18075,7 +18153,7 @@
         <v>25</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>1394</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="87" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18086,7 +18164,7 @@
         <v>0</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="F87" s="18" t="s">
         <v>17</v>
@@ -18095,7 +18173,7 @@
         <v>25</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>1396</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="88" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18106,7 +18184,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="F88" s="18" t="s">
         <v>17</v>
@@ -18115,7 +18193,7 @@
         <v>25</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>1398</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="89" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18126,7 +18204,7 @@
         <v>0</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="F89" s="18" t="s">
         <v>17</v>
@@ -18135,7 +18213,7 @@
         <v>25</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>1400</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="90" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18146,7 +18224,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="F90" s="18" t="s">
         <v>17</v>
@@ -18155,7 +18233,7 @@
         <v>25</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>1402</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="91" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18166,7 +18244,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="F91" s="18" t="s">
         <v>17</v>
@@ -18175,7 +18253,7 @@
         <v>25</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="92" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18186,7 +18264,7 @@
         <v>0</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="F92" s="18" t="s">
         <v>17</v>
@@ -18195,7 +18273,7 @@
         <v>25</v>
       </c>
       <c r="H92" s="24" t="s">
-        <v>1406</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="93" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18214,7 +18292,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="F94" s="18" t="s">
         <v>17</v>
@@ -18223,7 +18301,7 @@
         <v>25</v>
       </c>
       <c r="H94" s="24" t="s">
-        <v>1407</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="95" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18234,7 +18312,7 @@
         <v>0</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>1393</v>
+        <v>1399</v>
       </c>
       <c r="F95" s="18" t="s">
         <v>17</v>
@@ -18243,7 +18321,7 @@
         <v>25</v>
       </c>
       <c r="H95" s="24" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="96" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18254,7 +18332,7 @@
         <v>0</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>1395</v>
+        <v>1401</v>
       </c>
       <c r="F96" s="18" t="s">
         <v>17</v>
@@ -18263,7 +18341,7 @@
         <v>25</v>
       </c>
       <c r="H96" s="24" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="97" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18274,7 +18352,7 @@
         <v>0</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1397</v>
+        <v>1403</v>
       </c>
       <c r="F97" s="18" t="s">
         <v>17</v>
@@ -18283,7 +18361,7 @@
         <v>25</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="98" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18294,7 +18372,7 @@
         <v>0</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>1399</v>
+        <v>1405</v>
       </c>
       <c r="F98" s="18" t="s">
         <v>17</v>
@@ -18303,7 +18381,7 @@
         <v>25</v>
       </c>
       <c r="H98" s="24" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="99" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18314,7 +18392,7 @@
         <v>0</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>1401</v>
+        <v>1407</v>
       </c>
       <c r="F99" s="18" t="s">
         <v>17</v>
@@ -18323,7 +18401,7 @@
         <v>25</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>1412</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="100" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18334,7 +18412,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1403</v>
+        <v>1409</v>
       </c>
       <c r="F100" s="18" t="s">
         <v>17</v>
@@ -18343,7 +18421,7 @@
         <v>25</v>
       </c>
       <c r="H100" s="24" t="s">
-        <v>1413</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="101" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18354,7 +18432,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>1405</v>
+        <v>1411</v>
       </c>
       <c r="F101" s="18" t="s">
         <v>17</v>
@@ -18363,7 +18441,7 @@
         <v>25</v>
       </c>
       <c r="H101" s="24" t="s">
-        <v>1414</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18384,7 +18462,7 @@
     </row>
     <row r="104" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C104" s="18" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>1118</v>
@@ -18404,7 +18482,7 @@
     </row>
     <row r="105" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C105" s="18" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>1118</v>
@@ -18424,13 +18502,13 @@
     </row>
     <row r="106" customHeight="1" spans="3:8">
       <c r="C106" s="18" t="s">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="F106" s="18" t="s">
         <v>17</v>
@@ -18439,18 +18517,18 @@
         <v>1130</v>
       </c>
       <c r="H106" s="22" t="s">
-        <v>1419</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:8">
       <c r="C107" s="18" t="s">
-        <v>1420</v>
+        <v>1426</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>1421</v>
+        <v>1427</v>
       </c>
       <c r="F107" s="18" t="s">
         <v>17</v>
@@ -18459,18 +18537,18 @@
         <v>1130</v>
       </c>
       <c r="H107" s="22" t="s">
-        <v>1422</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:8">
       <c r="C108" s="18" t="s">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>1424</v>
+        <v>1430</v>
       </c>
       <c r="F108" s="18" t="s">
         <v>17</v>
@@ -18479,18 +18557,18 @@
         <v>1130</v>
       </c>
       <c r="H108" s="22" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:8">
       <c r="C109" s="18" t="s">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="F109" s="18" t="s">
         <v>17</v>
@@ -18499,47 +18577,47 @@
         <v>1130</v>
       </c>
       <c r="H109" s="22" t="s">
-        <v>1428</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:8">
       <c r="C111" s="18" t="s">
-        <v>1429</v>
+        <v>1435</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="F111" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G111" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H111" s="22" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:8">
       <c r="C112" s="18" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>1118</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="F112" s="18" t="s">
         <v>17</v>
       </c>
       <c r="G112" s="18" t="s">
-        <v>1242</v>
+        <v>1248</v>
       </c>
       <c r="H112" s="22" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="113" s="2" customFormat="1" customHeight="1" spans="3:8">
@@ -18552,182 +18630,182 @@
     </row>
     <row r="114" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C114" s="10" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="H114" s="18" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C115" s="10" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="H115" s="18" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C116" s="10" t="s">
-        <v>1442</v>
+        <v>1448</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E116" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G116" s="1" t="s">
         <v>1443</v>
       </c>
-      <c r="F116" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>1437</v>
-      </c>
       <c r="H116" s="18" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="117" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C117" s="10" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="H117" s="18" t="s">
-        <v>1447</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="118" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C118" s="10" t="s">
-        <v>1448</v>
+        <v>1454</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>1449</v>
+        <v>1455</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="H118" s="18" t="s">
-        <v>1450</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="119" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C119" s="10" t="s">
-        <v>1451</v>
+        <v>1457</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>1452</v>
+        <v>1458</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="H119" s="18" t="s">
-        <v>1453</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="120" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C120" s="10" t="s">
-        <v>1454</v>
+        <v>1460</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>1455</v>
+        <v>1461</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="H120" s="18" t="s">
-        <v>1456</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C121" s="10" t="s">
-        <v>1457</v>
+        <v>1463</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>1458</v>
+        <v>1464</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="H121" s="24" t="s">
-        <v>1459</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" customHeight="1" spans="3:8">
       <c r="C122" s="10" t="s">
-        <v>1460</v>
+        <v>1466</v>
       </c>
       <c r="D122" s="18" t="s">
         <v>47</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>1461</v>
+        <v>1467</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="H122" s="24" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -18738,16 +18816,16 @@
         <v>100</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>17</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="H123" s="24" t="s">
-        <v>1464</v>
+        <v>1470</v>
       </c>
     </row>
   </sheetData>
